--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -48,7 +48,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -415,14 +415,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
     <col width="28.25" customWidth="1" style="1" min="2" max="2"/>
     <col width="22.9140625" customWidth="1" style="1" min="3" max="3"/>
     <col width="37.6640625" customWidth="1" style="1" min="4" max="4"/>
-    <col width="8.6640625" customWidth="1" style="1" min="5" max="16384"/>
+    <col width="8.6640625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="8.6640625" customWidth="1" style="1" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -756,222 +757,1036 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:17:54</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>video_ng\violation_287_1786346266.avi</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:18:02</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>video_ng\violation_290_1786346273.avi</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:19:15</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>video_ng\violation_292_1786346349.avi</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:19:30</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>video_ng\violation_293_1786346362.avi</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:21:02</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>video_ng\violation_294_1786346454.avi</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:21:06</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>video_ng\violation_296_1786346458.avi</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:21:08</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>video_ng\violation_297_1786346461.avi</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:26:45</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>video_ok\violation_298_1786346797.avi</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:26:58</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>video_ok\violation_299_1786346810.avi</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>2026-08-10 14:27:05</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Camera_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>video_ok\violation_301_1786346816.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:35:36</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>video_ng\violation_316_1786347329.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:39:19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>video_ok\violation_324_1786347549.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:41:41</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>video_ng\violation_331_1786347694.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:43:06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>video_ng\violation_334_1786347778.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:43:06</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>video_ng\violation_335_1786347778.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:43:43</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>video_ok\violation_338_1786347816.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:44:22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>video_ng\violation_339_1786347848.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:44:22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>video_ng\violation_340_1786347847.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:45:19</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>video_ng\violation_347_1786347910.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:45:37</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>video_ng\violation_350_1786347929.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:45:38</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>video_ng\violation_353_1786347933.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:45:47</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>video_ng\violation_360_1786347939.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:46:52</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>video_ng\violation_361_1786348003.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:48:54</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>video_ng\violation_366_1786348125.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:49:24</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>video_ng\violation_367_1786348156.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:50:58</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>video_ng\violation_371_1786348251.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:51:38</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>video_ng\violation_373_1786348290.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:52:45</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>video_ng\violation_374_1786348357.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:52:52</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>video_ok\violation_375_1786348364.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:54:11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>video_ok\violation_380_1786348443.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:58:10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>video_ng\violation_383_1786348682.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:01:20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>video_ng\violation_394_1786348875.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:01:37</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>video_ng\violation_395_1786348890.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:02:19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>video_ok\violation_397_1786348923.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>video_ng\violation_411_1786348974.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>video_ng\violation_414_1786348977.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:04:46</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>video_ng\violation_424_1786349080.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:05:53</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>video_ng\violation_431_1786349146.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:06:43</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>video_ok\violation_434_1786349194.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:08:52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>video_ok\violation_435_1786349324.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:09:56</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>video_ng\violation_438_1786349388.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:11:42</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>video_ok\violation_440_1786349494.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:13:03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>video_ok\violation_441_1786349573.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:13:03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>video_ng\violation_444_1786349573.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:13:32</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>video_ng\violation_450_1786349605.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:14:22</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>video_ng\violation_455_1786349653.avi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:15:59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>video_ok\violation_457_1786349751.avi</t>
         </is>
       </c>
     </row>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -1790,6 +1790,160 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:51:48</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>video_ok\violation_787_1786355502.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:51:51</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>video_ng\violation_800_1786355506.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:51:53</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>video_ng\violation_808_1786355507.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:51:55</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>video_ng\violation_814_1786355509.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:52:23</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>video_ng\violation_818_1786355535.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:52:38</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>video_ok\violation_820_1786355549.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:53:05</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>video_ng\violation_822_1786355579.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -1944,6 +1944,72 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:13:09</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>video_ok\violation_825_1786410782.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:24:04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>video_ng\violation_842_1786411437.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:25:39</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>video_ng\violation_843_1786411530.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2010,6 +2010,50 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:02:11</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1020_1786590124.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:02:12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>video_ng\violation_1019_1786590125.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2010,6 +2010,292 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:27:22</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>video_ok\violation_16_1786879635.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:39:35</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>video_ok\violation_8_1786880368.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:39:42</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>video_ok\violation_14_1786880376.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:39:46</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>video_ok\violation_16_1786880380.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:39:48</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>video_ok\violation_23_1786880382.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:41:06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>video_ok\violation_7_1786880459.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:41:12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>video_ok\violation_14_1786880466.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:41:17</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>video_ok\violation_15_1786880471.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:42:21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>video_ok\violation_4_1786880535.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:42:27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>video_ok\violation_7_1786880540.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:42:34</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>video_ok\violation_14_1786880548.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:42:40</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>video_ok\violation_21_1786880554.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:43:17</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>video_ok\violation_45_1786880591.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2296,6 +2296,270 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:55:46</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1201_1786931738.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:57:16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1224_1786931829.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:02:57</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1250_1786932169.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:05:06</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1271_1786932298.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:07:43</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1284_1786932454.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:09:53</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1321_1786932586.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:11:27</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1339_1786932677.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:11:47</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1341_1786932686.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:11:55</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1350_1786932707.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:13:46</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1366_1786932816.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:14:47</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1371_1786932876.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:15:22</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>video_ok\violation_1379_1786932913.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2560,6 +2560,50 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:16:04</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Camera_3</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>video_ng\violation_49_1787130959.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:23:38</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Camera_3</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>video_ng\violation_43_1787131410.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2604,6 +2604,138 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:49:20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Camera_3</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>video_ng\violation_35_1787194152.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:49:27</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Camera_3</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>video_ng\violation_38_1787194158.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:58:13</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Camera_3</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>video_ng\violation_38_1787194687.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:58:15</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Camera_3</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>video_ng\violation_43_1787194690.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:58:17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Camera_3</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>video_ng\violation_46_1787194691.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:16:48</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Camera_3</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>video_ng\violation_35_1787195801.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2736,6 +2736,50 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:43:48</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>video_ng\violation_41_1787543021.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:43:50</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>video_ng\violation_42_1787543024.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2560,6 +2560,94 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-25 08:39:03</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>video_ng\violation_57_1787621935.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-25 08:40:59</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>video_ng\violation_61_1787622053.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-25 08:41:06</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>video_ok\violation_63_1787622058.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-25 08:41:09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>video_ng\violation_65_1787622061.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2648,6 +2648,204 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:07:09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>video_ng\violation_86_1787623621.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:07:57</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>video_ng\violation_93_1787623670.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:10:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>video_ok\violation_58_1787623793.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:10:02</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>video_ok\violation_59_1787623795.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:10:05</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>video_ng\violation_62_1787623799.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:10:45</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>video_ok\violation_64_1787623838.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:11:56</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>video_ng\violation_67_1787623911.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:14:54</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>video_ok\violation_87_1787624086.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:15:02</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>video_ng\violation_86_1787624094.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2846,6 +2846,72 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-27 09:12:07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>video_ng\violation_89_1787796720.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-27 09:18:51</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>video_ng\violation_90_1787797125.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-27 09:18:55</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>video_ng\violation_95_1787797128.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2912,6 +2912,270 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:01:08</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>video_ng\violation_120_1787803259.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:09:26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>video_ng\violation_122_1787803760.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:09:32</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>video_ng\violation_132_1787803766.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:09:34</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>video_ng\violation_136_1787803769.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:09:35</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>video_ng\violation_139_1787803770.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:09:38</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>video_ng\violation_137_1787803769.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:09:38</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>video_ng\violation_141_1787803772.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:09:47</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Camera_6</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>video_ng\violation_151_1787803781.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:47:24</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>video_ok\violation_185_1787806036.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:47:27</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>video_ok\violation_186_1787806038.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:48:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>video_ok\violation_191_1787806071.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:52:25</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>video_ok\violation_630_1787806336.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/video_history.xlsx
+++ b/logs/video_history.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.25" customWidth="1" style="1" min="1" max="1"/>
@@ -3176,6 +3176,116 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-01 11:41:12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>video_ok\violation_39756_1788237665.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-01 11:41:37</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>video_ok\violation_39759_1788237688.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-01 11:41:56</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>video_ok\violation_39770_1788237708.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-01 11:42:16</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>video_ok\violation_39772_1788237727.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-01 11:43:17</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>video_ok\violation_39780_1788237788.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
